--- a/tools/cloud-cost-management/cloud-finops-workbook.xlsx
+++ b/tools/cloud-cost-management/cloud-finops-workbook.xlsx
@@ -61,7 +61,7 @@
     <t>Reserved Capacity Break-Even</t>
   </si>
   <si>
-    <t>Model whether a commitment discount actually pays off at your real utilization rate, before you sign it.</t>
+    <t>Model whether a commitment discount pays off at your measured utilization rate, before you sign it.</t>
   </si>
   <si>
     <t>Showback / Chargeback</t>
@@ -196,7 +196,7 @@
     <t>Batch processing pool</t>
   </si>
   <si>
-    <t>If actual utilization is below the break-even line, the commitment is currently losing money versus paying on-demand for only what's used. Revisit before renewal, not after.</t>
+    <t>If measured utilization is below the break-even line, the commitment is currently losing money versus paying on-demand for only what's used. Revisit before renewal, not after.</t>
   </si>
   <si>
     <t>Tagged spend by team against total spend. The untagged gap is what governance is failing to attribute.</t>
@@ -283,7 +283,7 @@
     <t>Forecasting &amp; budgeting</t>
   </si>
   <si>
-    <t>Budgets set annually, not revisited when actuals drift</t>
+    <t>Budgets set annually and never revisited when actuals drift</t>
   </si>
   <si>
     <t>Unit economics</t>
